--- a/diseases/d043/2026-2029.xlsx
+++ b/diseases/d043/2026-2029.xlsx
@@ -25459,6 +25459,154 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>151</v>
+      </c>
+      <c r="O134" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.01068713244697751</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25492,7 +25640,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -25575,7 +25723,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -25585,7 +25733,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -25637,7 +25785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>765</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d043/2026-2029.xlsx
+++ b/diseases/d043/2026-2029.xlsx
@@ -25607,6 +25607,151 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25723,7 +25868,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -25733,7 +25878,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d043/2026-2029.xlsx
+++ b/diseases/d043/2026-2029.xlsx
@@ -23032,12 +23032,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -23071,10 +23071,10 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
@@ -23183,12 +23183,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -23222,10 +23222,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
@@ -23417,12 +23417,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -23456,10 +23456,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O123" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
@@ -23568,12 +23568,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -23607,10 +23607,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O124" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -23841,10 +23841,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
@@ -23953,12 +23953,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -23992,10 +23992,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
@@ -24187,12 +24187,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -24301,7 +24301,7 @@
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
@@ -24338,12 +24338,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -24424,7 +24424,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -24535,7 +24535,7 @@
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
@@ -24572,12 +24572,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -24611,10 +24611,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
@@ -24723,12 +24723,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -24762,10 +24762,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
@@ -24957,12 +24957,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -24996,10 +24996,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
@@ -25108,12 +25108,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -25147,10 +25147,10 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
@@ -25342,12 +25342,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -25386,76 +25386,82 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -25482,17 +25488,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -25517,93 +25523,179 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q134" t="n">
         <v>0</v>
       </c>
-      <c r="R134" t="n">
-        <v>0.01068713244697751</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -25665,12 +25757,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -25747,6 +25839,2994 @@
         </is>
       </c>
       <c r="BC135" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>151</v>
+      </c>
+      <c r="O136" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.01068713244697751</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CN-CQ</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Chongqing, China</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>13</v>
+      </c>
+      <c r="O139" t="n">
+        <v>13</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CN-GD</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Guangdong, China</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>13</v>
+      </c>
+      <c r="O140" t="n">
+        <v>13</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>9</v>
+      </c>
+      <c r="O141" t="n">
+        <v>9</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>9</v>
+      </c>
+      <c r="O142" t="n">
+        <v>9</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>16</v>
+      </c>
+      <c r="O147" t="n">
+        <v>16</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>16</v>
+      </c>
+      <c r="O148" t="n">
+        <v>16</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_TYPHUS; SER_CN_PROV_REPORT_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -25868,7 +28948,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -25878,7 +28958,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -25898,7 +28978,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -25930,7 +29010,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>916</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d043/2026-2029.xlsx
+++ b/diseases/d043/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4386,6 +4391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4534,6 +4544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8144,6 +8159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8292,6 +8312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11517,6 +11542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11665,6 +11695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14890,6 +14925,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15038,6 +15078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18648,6 +18693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18796,6 +18846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22021,6 +22076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22169,6 +22229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25779,6 +25844,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25927,6 +25997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28765,6 +28840,11 @@
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">

--- a/diseases/d043/2026-2029.xlsx
+++ b/diseases/d043/2026-2029.xlsx
@@ -2457,6 +2457,11 @@
       <c r="R14" t="n">
         <v>0.01355270280196709</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2469,12 +2474,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -4281,6 +4296,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4293,12 +4313,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5823,6 +5853,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5835,12 +5870,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -7647,6 +7692,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7659,12 +7709,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -9894,6 +9954,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9906,12 +9971,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -12000,6 +12075,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12012,12 +12092,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -14247,6 +14337,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14259,12 +14354,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15789,6 +15894,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15801,12 +15911,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16269,6 +16389,156 @@
       <c r="BC112" t="inlineStr">
         <is>
           <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>typhus</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -16398,7 +16668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
